--- a/Data/Taka/2025.xlsx
+++ b/Data/Taka/2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yossi\OneDrive\ドキュメント\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\yosi\#Webカスタマイズ\HealthControl\Data\Taka\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F817960E-9AF2-4F02-BFF7-EE371B33FB87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55809263-DBD1-4934-B864-95A10B10AB1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="500" yWindow="440" windowWidth="17370" windowHeight="9640" activeTab="5" xr2:uid="{231E781C-0F8F-447B-B2F4-43F56544C5E8}"/>
+    <workbookView xWindow="2800" yWindow="0" windowWidth="15550" windowHeight="10080" activeTab="2" xr2:uid="{231E781C-0F8F-447B-B2F4-43F56544C5E8}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="9" r:id="rId1"/>
@@ -6759,7 +6759,7 @@
         <v>45.95</v>
       </c>
       <c r="Y14" s="27">
-        <v>26.35</v>
+        <v>46.35</v>
       </c>
       <c r="Z14" s="27">
         <v>46</v>

--- a/Data/Taka/2025.xlsx
+++ b/Data/Taka/2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\yosi\#Webカスタマイズ\HealthControl\Data\Taka\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4fd38d413068b4cb/ドキュメント/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55809263-DBD1-4934-B864-95A10B10AB1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="13_ncr:1_{1060BED3-675B-4811-A71E-B1F601C85309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B15F561-E754-4D26-B269-C915AFD7B4C3}"/>
   <bookViews>
-    <workbookView xWindow="2800" yWindow="0" windowWidth="15550" windowHeight="10080" activeTab="2" xr2:uid="{231E781C-0F8F-447B-B2F4-43F56544C5E8}"/>
+    <workbookView xWindow="2390" yWindow="0" windowWidth="15550" windowHeight="10080" activeTab="5" xr2:uid="{231E781C-0F8F-447B-B2F4-43F56544C5E8}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="9" r:id="rId1"/>
@@ -1167,6 +1167,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -11089,26 +11093,66 @@
       <c r="H7" s="13">
         <v>107</v>
       </c>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="13"/>
-      <c r="S7" s="13"/>
-      <c r="T7" s="13"/>
-      <c r="U7" s="13"/>
-      <c r="V7" s="13"/>
-      <c r="W7" s="13"/>
-      <c r="X7" s="13"/>
-      <c r="Y7" s="13"/>
-      <c r="Z7" s="13"/>
-      <c r="AA7" s="13"/>
-      <c r="AB7" s="14"/>
+      <c r="I7" s="13">
+        <v>101</v>
+      </c>
+      <c r="J7" s="13">
+        <v>102</v>
+      </c>
+      <c r="K7" s="13">
+        <v>104</v>
+      </c>
+      <c r="L7" s="13">
+        <v>100</v>
+      </c>
+      <c r="M7" s="13">
+        <v>104</v>
+      </c>
+      <c r="N7" s="47">
+        <v>99</v>
+      </c>
+      <c r="O7" s="13">
+        <v>108</v>
+      </c>
+      <c r="P7" s="13">
+        <v>108</v>
+      </c>
+      <c r="Q7" s="13">
+        <v>101</v>
+      </c>
+      <c r="R7" s="13">
+        <v>111</v>
+      </c>
+      <c r="S7" s="13">
+        <v>106</v>
+      </c>
+      <c r="T7" s="13">
+        <v>104</v>
+      </c>
+      <c r="U7" s="13">
+        <v>106</v>
+      </c>
+      <c r="V7" s="13">
+        <v>104</v>
+      </c>
+      <c r="W7" s="13">
+        <v>110</v>
+      </c>
+      <c r="X7" s="13">
+        <v>105</v>
+      </c>
+      <c r="Y7" s="13">
+        <v>100</v>
+      </c>
+      <c r="Z7" s="47">
+        <v>94</v>
+      </c>
+      <c r="AA7" s="13">
+        <v>104</v>
+      </c>
+      <c r="AB7" s="14">
+        <v>106</v>
+      </c>
       <c r="AC7" s="13"/>
       <c r="AD7" s="13"/>
       <c r="AE7" s="13"/>
@@ -11136,26 +11180,66 @@
       <c r="H8" s="13">
         <v>65</v>
       </c>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="13"/>
-      <c r="S8" s="13"/>
-      <c r="T8" s="13"/>
-      <c r="U8" s="13"/>
-      <c r="V8" s="13"/>
-      <c r="W8" s="13"/>
-      <c r="X8" s="13"/>
-      <c r="Y8" s="13"/>
-      <c r="Z8" s="13"/>
-      <c r="AA8" s="13"/>
-      <c r="AB8" s="13"/>
+      <c r="I8" s="13">
+        <v>63</v>
+      </c>
+      <c r="J8" s="13">
+        <v>60</v>
+      </c>
+      <c r="K8" s="13">
+        <v>64</v>
+      </c>
+      <c r="L8" s="13">
+        <v>61</v>
+      </c>
+      <c r="M8" s="13">
+        <v>61</v>
+      </c>
+      <c r="N8" s="47">
+        <v>58</v>
+      </c>
+      <c r="O8" s="13">
+        <v>61</v>
+      </c>
+      <c r="P8" s="13">
+        <v>70</v>
+      </c>
+      <c r="Q8" s="13">
+        <v>64</v>
+      </c>
+      <c r="R8" s="13">
+        <v>68</v>
+      </c>
+      <c r="S8" s="13">
+        <v>65</v>
+      </c>
+      <c r="T8" s="13">
+        <v>63</v>
+      </c>
+      <c r="U8" s="13">
+        <v>66</v>
+      </c>
+      <c r="V8" s="47">
+        <v>59</v>
+      </c>
+      <c r="W8" s="13">
+        <v>67</v>
+      </c>
+      <c r="X8" s="13">
+        <v>63</v>
+      </c>
+      <c r="Y8" s="13">
+        <v>61</v>
+      </c>
+      <c r="Z8" s="13">
+        <v>61</v>
+      </c>
+      <c r="AA8" s="13">
+        <v>64</v>
+      </c>
+      <c r="AB8" s="13">
+        <v>67</v>
+      </c>
       <c r="AC8" s="13"/>
       <c r="AD8" s="13"/>
       <c r="AE8" s="13"/>
@@ -11183,26 +11267,66 @@
       <c r="H9" s="9">
         <v>36.5</v>
       </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="9"/>
-      <c r="S9" s="9"/>
-      <c r="T9" s="9"/>
-      <c r="U9" s="9"/>
-      <c r="V9" s="9"/>
-      <c r="W9" s="9"/>
-      <c r="X9" s="9"/>
-      <c r="Y9" s="9"/>
-      <c r="Z9" s="9"/>
-      <c r="AA9" s="9"/>
-      <c r="AB9" s="9"/>
+      <c r="I9" s="9">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="J9" s="9">
+        <v>36.5</v>
+      </c>
+      <c r="K9" s="9">
+        <v>36.4</v>
+      </c>
+      <c r="L9" s="9">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="M9" s="9">
+        <v>36.5</v>
+      </c>
+      <c r="N9" s="9">
+        <v>36.5</v>
+      </c>
+      <c r="O9" s="9">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="P9" s="9">
+        <v>36.1</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="R9" s="9">
+        <v>36.4</v>
+      </c>
+      <c r="S9" s="9">
+        <v>36.6</v>
+      </c>
+      <c r="T9" s="9">
+        <v>36.1</v>
+      </c>
+      <c r="U9" s="9">
+        <v>36.5</v>
+      </c>
+      <c r="V9" s="9">
+        <v>36.6</v>
+      </c>
+      <c r="W9" s="9">
+        <v>36.1</v>
+      </c>
+      <c r="X9" s="9">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="Y9" s="9">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="Z9" s="9">
+        <v>36.6</v>
+      </c>
+      <c r="AA9" s="9">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="AB9" s="9">
+        <v>36.5</v>
+      </c>
       <c r="AC9" s="9"/>
       <c r="AD9" s="9"/>
       <c r="AE9" s="9"/>
@@ -11230,26 +11354,66 @@
       <c r="H10" s="10">
         <v>96</v>
       </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10"/>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="10"/>
-      <c r="S10" s="10"/>
-      <c r="T10" s="10"/>
-      <c r="U10" s="10"/>
-      <c r="V10" s="10"/>
-      <c r="W10" s="10"/>
-      <c r="X10" s="10"/>
-      <c r="Y10" s="10"/>
-      <c r="Z10" s="10"/>
-      <c r="AA10" s="10"/>
-      <c r="AB10" s="10"/>
+      <c r="I10" s="10">
+        <v>96</v>
+      </c>
+      <c r="J10" s="10">
+        <v>98</v>
+      </c>
+      <c r="K10" s="10">
+        <v>96</v>
+      </c>
+      <c r="L10" s="10">
+        <v>96</v>
+      </c>
+      <c r="M10" s="10">
+        <v>97</v>
+      </c>
+      <c r="N10" s="10">
+        <v>97</v>
+      </c>
+      <c r="O10" s="10">
+        <v>97</v>
+      </c>
+      <c r="P10" s="10">
+        <v>97</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>98</v>
+      </c>
+      <c r="R10" s="10">
+        <v>96</v>
+      </c>
+      <c r="S10" s="10">
+        <v>97</v>
+      </c>
+      <c r="T10" s="10">
+        <v>96</v>
+      </c>
+      <c r="U10" s="10">
+        <v>98</v>
+      </c>
+      <c r="V10" s="10">
+        <v>98</v>
+      </c>
+      <c r="W10" s="10">
+        <v>96</v>
+      </c>
+      <c r="X10" s="10">
+        <v>98</v>
+      </c>
+      <c r="Y10" s="10">
+        <v>96</v>
+      </c>
+      <c r="Z10" s="10">
+        <v>97</v>
+      </c>
+      <c r="AA10" s="10">
+        <v>97</v>
+      </c>
+      <c r="AB10" s="10">
+        <v>96</v>
+      </c>
       <c r="AC10" s="10"/>
       <c r="AD10" s="10"/>
       <c r="AE10" s="10"/>
@@ -11277,26 +11441,66 @@
       <c r="H11" s="11">
         <v>70</v>
       </c>
-      <c r="I11" s="11"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="12"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
-      <c r="V11" s="11"/>
-      <c r="W11" s="11"/>
-      <c r="X11" s="11"/>
-      <c r="Y11" s="11"/>
-      <c r="Z11" s="11"/>
-      <c r="AA11" s="11"/>
-      <c r="AB11" s="12"/>
+      <c r="I11" s="11">
+        <v>71</v>
+      </c>
+      <c r="J11" s="12">
+        <v>65</v>
+      </c>
+      <c r="K11" s="11">
+        <v>66</v>
+      </c>
+      <c r="L11" s="11">
+        <v>67</v>
+      </c>
+      <c r="M11" s="11">
+        <v>69</v>
+      </c>
+      <c r="N11" s="11">
+        <v>68</v>
+      </c>
+      <c r="O11" s="11">
+        <v>68</v>
+      </c>
+      <c r="P11" s="11">
+        <v>70</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>71</v>
+      </c>
+      <c r="R11" s="12">
+        <v>72</v>
+      </c>
+      <c r="S11" s="11">
+        <v>74</v>
+      </c>
+      <c r="T11" s="11">
+        <v>70</v>
+      </c>
+      <c r="U11" s="11">
+        <v>72</v>
+      </c>
+      <c r="V11" s="11">
+        <v>71</v>
+      </c>
+      <c r="W11" s="11">
+        <v>75</v>
+      </c>
+      <c r="X11" s="11">
+        <v>78</v>
+      </c>
+      <c r="Y11" s="11">
+        <v>72</v>
+      </c>
+      <c r="Z11" s="11">
+        <v>70</v>
+      </c>
+      <c r="AA11" s="11">
+        <v>70</v>
+      </c>
+      <c r="AB11" s="12">
+        <v>68</v>
+      </c>
       <c r="AC11" s="11"/>
       <c r="AD11" s="11"/>
       <c r="AE11" s="11"/>
@@ -11324,26 +11528,66 @@
       <c r="H12" s="26">
         <v>63.4</v>
       </c>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
-      <c r="K12" s="26"/>
-      <c r="L12" s="26"/>
-      <c r="M12" s="26"/>
-      <c r="N12" s="26"/>
-      <c r="O12" s="26"/>
-      <c r="P12" s="26"/>
-      <c r="Q12" s="26"/>
-      <c r="R12" s="26"/>
-      <c r="S12" s="26"/>
-      <c r="T12" s="26"/>
-      <c r="U12" s="26"/>
-      <c r="V12" s="26"/>
-      <c r="W12" s="26"/>
-      <c r="X12" s="26"/>
-      <c r="Y12" s="26"/>
-      <c r="Z12" s="26"/>
-      <c r="AA12" s="26"/>
-      <c r="AB12" s="26"/>
+      <c r="I12" s="26">
+        <v>63.05</v>
+      </c>
+      <c r="J12" s="26">
+        <v>63.25</v>
+      </c>
+      <c r="K12" s="26">
+        <v>63.55</v>
+      </c>
+      <c r="L12" s="26">
+        <v>63.65</v>
+      </c>
+      <c r="M12" s="26">
+        <v>63.6</v>
+      </c>
+      <c r="N12" s="26">
+        <v>64.05</v>
+      </c>
+      <c r="O12" s="26">
+        <v>63.7</v>
+      </c>
+      <c r="P12" s="26">
+        <v>63.7</v>
+      </c>
+      <c r="Q12" s="26">
+        <v>63.7</v>
+      </c>
+      <c r="R12" s="26">
+        <v>63.95</v>
+      </c>
+      <c r="S12" s="26">
+        <v>63.65</v>
+      </c>
+      <c r="T12" s="26">
+        <v>63.7</v>
+      </c>
+      <c r="U12" s="26">
+        <v>63.6</v>
+      </c>
+      <c r="V12" s="26">
+        <v>63.7</v>
+      </c>
+      <c r="W12" s="26">
+        <v>63.05</v>
+      </c>
+      <c r="X12" s="26">
+        <v>63.2</v>
+      </c>
+      <c r="Y12" s="26">
+        <v>63.4</v>
+      </c>
+      <c r="Z12" s="26">
+        <v>62.25</v>
+      </c>
+      <c r="AA12" s="26">
+        <v>62.7</v>
+      </c>
+      <c r="AB12" s="26">
+        <v>63.4</v>
+      </c>
       <c r="AC12" s="26"/>
       <c r="AD12" s="26"/>
       <c r="AE12" s="26"/>
@@ -11371,26 +11615,66 @@
       <c r="H13" s="27">
         <v>22.4</v>
       </c>
-      <c r="I13" s="27"/>
-      <c r="J13" s="27"/>
-      <c r="K13" s="27"/>
-      <c r="L13" s="27"/>
-      <c r="M13" s="27"/>
-      <c r="N13" s="27"/>
-      <c r="O13" s="27"/>
-      <c r="P13" s="27"/>
-      <c r="Q13" s="27"/>
-      <c r="R13" s="27"/>
-      <c r="S13" s="27"/>
-      <c r="T13" s="27"/>
-      <c r="U13" s="27"/>
-      <c r="V13" s="27"/>
-      <c r="W13" s="27"/>
-      <c r="X13" s="27"/>
-      <c r="Y13" s="27"/>
-      <c r="Z13" s="27"/>
-      <c r="AA13" s="27"/>
-      <c r="AB13" s="27"/>
+      <c r="I13" s="27">
+        <v>22.2</v>
+      </c>
+      <c r="J13" s="27">
+        <v>22.5</v>
+      </c>
+      <c r="K13" s="27">
+        <v>23</v>
+      </c>
+      <c r="L13" s="27">
+        <v>22</v>
+      </c>
+      <c r="M13" s="27">
+        <v>21.6</v>
+      </c>
+      <c r="N13" s="27">
+        <v>22.2</v>
+      </c>
+      <c r="O13" s="27">
+        <v>21.8</v>
+      </c>
+      <c r="P13" s="27">
+        <v>22.2</v>
+      </c>
+      <c r="Q13" s="27">
+        <v>21.9</v>
+      </c>
+      <c r="R13" s="27">
+        <v>22.1</v>
+      </c>
+      <c r="S13" s="27">
+        <v>22.4</v>
+      </c>
+      <c r="T13" s="27">
+        <v>22.4</v>
+      </c>
+      <c r="U13" s="27">
+        <v>22.2</v>
+      </c>
+      <c r="V13" s="27">
+        <v>22.1</v>
+      </c>
+      <c r="W13" s="27">
+        <v>21.9</v>
+      </c>
+      <c r="X13" s="27">
+        <v>23</v>
+      </c>
+      <c r="Y13" s="27">
+        <v>22.1</v>
+      </c>
+      <c r="Z13" s="27">
+        <v>22.3</v>
+      </c>
+      <c r="AA13" s="27">
+        <v>22.6</v>
+      </c>
+      <c r="AB13" s="27">
+        <v>22.5</v>
+      </c>
       <c r="AC13" s="27"/>
       <c r="AD13" s="27"/>
       <c r="AE13" s="27"/>
@@ -11418,26 +11702,66 @@
       <c r="H14" s="27">
         <v>46.9</v>
       </c>
-      <c r="I14" s="27"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="27"/>
-      <c r="L14" s="27"/>
-      <c r="M14" s="27"/>
-      <c r="N14" s="27"/>
-      <c r="O14" s="27"/>
-      <c r="P14" s="27"/>
-      <c r="Q14" s="27"/>
-      <c r="R14" s="27"/>
-      <c r="S14" s="27"/>
-      <c r="T14" s="27"/>
-      <c r="U14" s="27"/>
-      <c r="V14" s="27"/>
-      <c r="W14" s="27"/>
-      <c r="X14" s="27"/>
-      <c r="Y14" s="27"/>
-      <c r="Z14" s="27"/>
-      <c r="AA14" s="27"/>
-      <c r="AB14" s="27"/>
+      <c r="I14" s="27">
+        <v>46.75</v>
+      </c>
+      <c r="J14" s="27">
+        <v>46.7</v>
+      </c>
+      <c r="K14" s="27">
+        <v>46.65</v>
+      </c>
+      <c r="L14" s="27">
+        <v>47.3</v>
+      </c>
+      <c r="M14" s="27">
+        <v>47.45</v>
+      </c>
+      <c r="N14" s="27">
+        <v>47.45</v>
+      </c>
+      <c r="O14" s="27">
+        <v>47.45</v>
+      </c>
+      <c r="P14" s="27">
+        <v>47.2</v>
+      </c>
+      <c r="Q14" s="27">
+        <v>47.35</v>
+      </c>
+      <c r="R14" s="27">
+        <v>47.45</v>
+      </c>
+      <c r="S14" s="27">
+        <v>47</v>
+      </c>
+      <c r="T14" s="27">
+        <v>47.05</v>
+      </c>
+      <c r="U14" s="27">
+        <v>47.15</v>
+      </c>
+      <c r="V14" s="27">
+        <v>46.85</v>
+      </c>
+      <c r="W14" s="27">
+        <v>46.9</v>
+      </c>
+      <c r="X14" s="27">
+        <v>46.35</v>
+      </c>
+      <c r="Y14" s="27">
+        <v>47</v>
+      </c>
+      <c r="Z14" s="27">
+        <v>46.3</v>
+      </c>
+      <c r="AA14" s="27">
+        <v>46.2</v>
+      </c>
+      <c r="AB14" s="27">
+        <v>46.8</v>
+      </c>
       <c r="AC14" s="27"/>
       <c r="AD14" s="27"/>
       <c r="AE14" s="27"/>
@@ -11465,26 +11789,66 @@
       <c r="H15" s="27">
         <v>2.6</v>
       </c>
-      <c r="I15" s="27"/>
-      <c r="J15" s="27"/>
-      <c r="K15" s="27"/>
-      <c r="L15" s="27"/>
-      <c r="M15" s="27"/>
-      <c r="N15" s="27"/>
-      <c r="O15" s="27"/>
-      <c r="P15" s="27"/>
-      <c r="Q15" s="27"/>
-      <c r="R15" s="27"/>
-      <c r="S15" s="27"/>
-      <c r="T15" s="27"/>
-      <c r="U15" s="27"/>
-      <c r="V15" s="27"/>
-      <c r="W15" s="27"/>
-      <c r="X15" s="27"/>
-      <c r="Y15" s="27"/>
-      <c r="Z15" s="27"/>
-      <c r="AA15" s="27"/>
-      <c r="AB15" s="27"/>
+      <c r="I15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="J15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="K15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="L15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="M15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="N15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="O15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="P15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="Q15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="R15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="S15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="T15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="U15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="V15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="W15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="X15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="Y15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="Z15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="AA15" s="27">
+        <v>2.5</v>
+      </c>
+      <c r="AB15" s="27">
+        <v>2.6</v>
+      </c>
       <c r="AC15" s="27"/>
       <c r="AD15" s="27"/>
       <c r="AE15" s="27"/>
@@ -11512,26 +11876,66 @@
       <c r="H16" s="27">
         <v>13</v>
       </c>
-      <c r="I16" s="27"/>
-      <c r="J16" s="27"/>
-      <c r="K16" s="27"/>
-      <c r="L16" s="27"/>
-      <c r="M16" s="27"/>
-      <c r="N16" s="27"/>
-      <c r="O16" s="27"/>
-      <c r="P16" s="27"/>
-      <c r="Q16" s="27"/>
-      <c r="R16" s="27"/>
-      <c r="S16" s="27"/>
-      <c r="T16" s="27"/>
-      <c r="U16" s="27"/>
-      <c r="V16" s="27"/>
-      <c r="W16" s="27"/>
-      <c r="X16" s="27"/>
-      <c r="Y16" s="27"/>
-      <c r="Z16" s="27"/>
-      <c r="AA16" s="27"/>
-      <c r="AB16" s="27"/>
+      <c r="I16" s="27">
+        <v>12.5</v>
+      </c>
+      <c r="J16" s="27">
+        <v>13</v>
+      </c>
+      <c r="K16" s="27">
+        <v>13</v>
+      </c>
+      <c r="L16" s="27">
+        <v>13</v>
+      </c>
+      <c r="M16" s="27">
+        <v>12.5</v>
+      </c>
+      <c r="N16" s="27">
+        <v>13</v>
+      </c>
+      <c r="O16" s="27">
+        <v>13</v>
+      </c>
+      <c r="P16" s="27">
+        <v>13</v>
+      </c>
+      <c r="Q16" s="27">
+        <v>13</v>
+      </c>
+      <c r="R16" s="27">
+        <v>13</v>
+      </c>
+      <c r="S16" s="27">
+        <v>13</v>
+      </c>
+      <c r="T16" s="27">
+        <v>13</v>
+      </c>
+      <c r="U16" s="27">
+        <v>13</v>
+      </c>
+      <c r="V16" s="27">
+        <v>13</v>
+      </c>
+      <c r="W16" s="27">
+        <v>12.5</v>
+      </c>
+      <c r="X16" s="27">
+        <v>13</v>
+      </c>
+      <c r="Y16" s="27">
+        <v>13</v>
+      </c>
+      <c r="Z16" s="27">
+        <v>12.5</v>
+      </c>
+      <c r="AA16" s="27">
+        <v>12.5</v>
+      </c>
+      <c r="AB16" s="27">
+        <v>13</v>
+      </c>
       <c r="AC16" s="27"/>
       <c r="AD16" s="27"/>
       <c r="AE16" s="27"/>
@@ -11559,26 +11963,66 @@
       <c r="H17" s="23">
         <v>1334</v>
       </c>
-      <c r="I17" s="23"/>
-      <c r="J17" s="23"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="23"/>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
-      <c r="S17" s="23"/>
-      <c r="T17" s="23"/>
-      <c r="U17" s="23"/>
-      <c r="V17" s="23"/>
-      <c r="W17" s="23"/>
-      <c r="X17" s="23"/>
-      <c r="Y17" s="23"/>
-      <c r="Z17" s="23"/>
-      <c r="AA17" s="23"/>
-      <c r="AB17" s="23"/>
+      <c r="I17" s="23">
+        <v>1329</v>
+      </c>
+      <c r="J17" s="23">
+        <v>1328</v>
+      </c>
+      <c r="K17" s="23">
+        <v>1327</v>
+      </c>
+      <c r="L17" s="23">
+        <v>1346</v>
+      </c>
+      <c r="M17" s="23">
+        <v>1350</v>
+      </c>
+      <c r="N17" s="23">
+        <v>1351</v>
+      </c>
+      <c r="O17" s="23">
+        <v>1349</v>
+      </c>
+      <c r="P17" s="23">
+        <v>1343</v>
+      </c>
+      <c r="Q17" s="23">
+        <v>1347</v>
+      </c>
+      <c r="R17" s="23">
+        <v>1350</v>
+      </c>
+      <c r="S17" s="23">
+        <v>1338</v>
+      </c>
+      <c r="T17" s="23">
+        <v>1339</v>
+      </c>
+      <c r="U17" s="23">
+        <v>1341</v>
+      </c>
+      <c r="V17" s="23">
+        <v>1334</v>
+      </c>
+      <c r="W17" s="23">
+        <v>1333</v>
+      </c>
+      <c r="X17" s="23">
+        <v>1319</v>
+      </c>
+      <c r="Y17" s="23">
+        <v>1338</v>
+      </c>
+      <c r="Z17" s="23">
+        <v>1316</v>
+      </c>
+      <c r="AA17" s="23">
+        <v>1313</v>
+      </c>
+      <c r="AB17" s="23">
+        <v>1331</v>
+      </c>
       <c r="AC17" s="23"/>
       <c r="AD17" s="23"/>
       <c r="AE17" s="23"/>
@@ -11603,26 +12047,66 @@
       <c r="G18" s="30">
         <v>4568</v>
       </c>
-      <c r="H18" s="30"/>
-      <c r="I18" s="30"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="30"/>
-      <c r="L18" s="30"/>
-      <c r="M18" s="30"/>
-      <c r="N18" s="30"/>
-      <c r="O18" s="30"/>
-      <c r="P18" s="30"/>
-      <c r="Q18" s="30"/>
-      <c r="R18" s="30"/>
-      <c r="S18" s="30"/>
-      <c r="T18" s="30"/>
-      <c r="U18" s="30"/>
-      <c r="V18" s="30"/>
-      <c r="W18" s="30"/>
-      <c r="X18" s="30"/>
-      <c r="Y18" s="30"/>
-      <c r="Z18" s="30"/>
-      <c r="AA18" s="30"/>
+      <c r="H18" s="30">
+        <v>1500</v>
+      </c>
+      <c r="I18" s="30">
+        <v>63</v>
+      </c>
+      <c r="J18" s="30">
+        <v>2655</v>
+      </c>
+      <c r="K18" s="30">
+        <v>4545</v>
+      </c>
+      <c r="L18" s="30">
+        <v>2789</v>
+      </c>
+      <c r="M18" s="30">
+        <v>4738</v>
+      </c>
+      <c r="N18" s="30">
+        <v>4952</v>
+      </c>
+      <c r="O18" s="30">
+        <v>18</v>
+      </c>
+      <c r="P18" s="30">
+        <v>2761</v>
+      </c>
+      <c r="Q18" s="30">
+        <v>2775</v>
+      </c>
+      <c r="R18" s="30">
+        <v>4567</v>
+      </c>
+      <c r="S18" s="30">
+        <v>12</v>
+      </c>
+      <c r="T18" s="30">
+        <v>2237</v>
+      </c>
+      <c r="U18" s="30">
+        <v>4616</v>
+      </c>
+      <c r="V18" s="30">
+        <v>365</v>
+      </c>
+      <c r="W18" s="30">
+        <v>1725</v>
+      </c>
+      <c r="X18" s="30">
+        <v>2349</v>
+      </c>
+      <c r="Y18" s="30">
+        <v>3369</v>
+      </c>
+      <c r="Z18" s="30">
+        <v>4573</v>
+      </c>
+      <c r="AA18" s="30">
+        <v>4725</v>
+      </c>
       <c r="AB18" s="30"/>
       <c r="AC18" s="30"/>
       <c r="AD18" s="30"/>

--- a/Data/Taka/2025.xlsx
+++ b/Data/Taka/2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4fd38d413068b4cb/ドキュメント/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yossi\OneDrive\ドキュメント\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="13_ncr:1_{1060BED3-675B-4811-A71E-B1F601C85309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B15F561-E754-4D26-B269-C915AFD7B4C3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C99DBEB-441F-4CD1-BA62-3E989C709E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2390" yWindow="0" windowWidth="15550" windowHeight="10080" activeTab="5" xr2:uid="{231E781C-0F8F-447B-B2F4-43F56544C5E8}"/>
+    <workbookView xWindow="230" yWindow="0" windowWidth="18140" windowHeight="10080" activeTab="7" xr2:uid="{231E781C-0F8F-447B-B2F4-43F56544C5E8}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="9" r:id="rId1"/>
@@ -19,6 +19,8 @@
     <sheet name="4" sheetId="12" r:id="rId4"/>
     <sheet name="5" sheetId="13" r:id="rId5"/>
     <sheet name="6" sheetId="14" r:id="rId6"/>
+    <sheet name="7" sheetId="15" r:id="rId7"/>
+    <sheet name="8" sheetId="16" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'1'!$A$1:$AG$41</definedName>
@@ -27,6 +29,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">'4'!$A$1:$AH$35</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'5'!$A$1:$AG$35</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'6'!$A$1:$AH$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'7'!$A$1:$AG$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'8'!$A$1:$AG$35</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -47,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="40">
   <si>
     <t>家庭内健康管理(孝則)</t>
     <rPh sb="0" eb="3">
@@ -1167,10 +1171,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -11153,10 +11153,18 @@
       <c r="AB7" s="14">
         <v>106</v>
       </c>
-      <c r="AC7" s="13"/>
-      <c r="AD7" s="13"/>
-      <c r="AE7" s="13"/>
-      <c r="AF7" s="13"/>
+      <c r="AC7" s="13">
+        <v>113</v>
+      </c>
+      <c r="AD7" s="13">
+        <v>102</v>
+      </c>
+      <c r="AE7" s="13">
+        <v>106</v>
+      </c>
+      <c r="AF7" s="13">
+        <v>102</v>
+      </c>
     </row>
     <row r="8" spans="2:32" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="15" t="s">
@@ -11240,10 +11248,18 @@
       <c r="AB8" s="13">
         <v>67</v>
       </c>
-      <c r="AC8" s="13"/>
-      <c r="AD8" s="13"/>
-      <c r="AE8" s="13"/>
-      <c r="AF8" s="13"/>
+      <c r="AC8" s="13">
+        <v>64</v>
+      </c>
+      <c r="AD8" s="13">
+        <v>60</v>
+      </c>
+      <c r="AE8" s="13">
+        <v>63</v>
+      </c>
+      <c r="AF8" s="13">
+        <v>64</v>
+      </c>
     </row>
     <row r="9" spans="2:32" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="5" t="s">
@@ -11327,10 +11343,18 @@
       <c r="AB9" s="9">
         <v>36.5</v>
       </c>
-      <c r="AC9" s="9"/>
-      <c r="AD9" s="9"/>
-      <c r="AE9" s="9"/>
-      <c r="AF9" s="9"/>
+      <c r="AC9" s="9">
+        <v>36.6</v>
+      </c>
+      <c r="AD9" s="9">
+        <v>36.5</v>
+      </c>
+      <c r="AE9" s="9">
+        <v>36.5</v>
+      </c>
+      <c r="AF9" s="9">
+        <v>36.6</v>
+      </c>
     </row>
     <row r="10" spans="2:32" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="5" t="s">
@@ -11414,10 +11438,18 @@
       <c r="AB10" s="10">
         <v>96</v>
       </c>
-      <c r="AC10" s="10"/>
-      <c r="AD10" s="10"/>
-      <c r="AE10" s="10"/>
-      <c r="AF10" s="10"/>
+      <c r="AC10" s="10">
+        <v>97</v>
+      </c>
+      <c r="AD10" s="10">
+        <v>98</v>
+      </c>
+      <c r="AE10" s="10">
+        <v>95</v>
+      </c>
+      <c r="AF10" s="10">
+        <v>97</v>
+      </c>
     </row>
     <row r="11" spans="2:32" ht="14" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B11" s="7" t="s">
@@ -11501,10 +11533,18 @@
       <c r="AB11" s="12">
         <v>68</v>
       </c>
-      <c r="AC11" s="11"/>
-      <c r="AD11" s="11"/>
-      <c r="AE11" s="11"/>
-      <c r="AF11" s="11"/>
+      <c r="AC11" s="11">
+        <v>71</v>
+      </c>
+      <c r="AD11" s="11">
+        <v>67</v>
+      </c>
+      <c r="AE11" s="11">
+        <v>65</v>
+      </c>
+      <c r="AF11" s="11">
+        <v>67</v>
+      </c>
     </row>
     <row r="12" spans="2:32" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="24" t="s">
@@ -11588,10 +11628,18 @@
       <c r="AB12" s="26">
         <v>63.4</v>
       </c>
-      <c r="AC12" s="26"/>
-      <c r="AD12" s="26"/>
-      <c r="AE12" s="26"/>
-      <c r="AF12" s="26"/>
+      <c r="AC12" s="26">
+        <v>63.7</v>
+      </c>
+      <c r="AD12" s="26">
+        <v>63.7</v>
+      </c>
+      <c r="AE12" s="26">
+        <v>64.3</v>
+      </c>
+      <c r="AF12" s="26">
+        <v>64.05</v>
+      </c>
     </row>
     <row r="13" spans="2:32" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="25" t="s">
@@ -11675,10 +11723,18 @@
       <c r="AB13" s="27">
         <v>22.5</v>
       </c>
-      <c r="AC13" s="27"/>
-      <c r="AD13" s="27"/>
-      <c r="AE13" s="27"/>
-      <c r="AF13" s="27"/>
+      <c r="AC13" s="27">
+        <v>22.4</v>
+      </c>
+      <c r="AD13" s="27">
+        <v>22.6</v>
+      </c>
+      <c r="AE13" s="27">
+        <v>23</v>
+      </c>
+      <c r="AF13" s="27">
+        <v>22.9</v>
+      </c>
     </row>
     <row r="14" spans="2:32" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="25" t="s">
@@ -11762,10 +11818,18 @@
       <c r="AB14" s="27">
         <v>46.8</v>
       </c>
-      <c r="AC14" s="27"/>
-      <c r="AD14" s="27"/>
-      <c r="AE14" s="27"/>
-      <c r="AF14" s="27"/>
+      <c r="AC14" s="27">
+        <v>47.1</v>
+      </c>
+      <c r="AD14" s="27">
+        <v>46.95</v>
+      </c>
+      <c r="AE14" s="27">
+        <v>47.15</v>
+      </c>
+      <c r="AF14" s="27">
+        <v>47.05</v>
+      </c>
     </row>
     <row r="15" spans="2:32" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="25" t="s">
@@ -11849,10 +11913,18 @@
       <c r="AB15" s="27">
         <v>2.6</v>
       </c>
-      <c r="AC15" s="27"/>
-      <c r="AD15" s="27"/>
-      <c r="AE15" s="27"/>
-      <c r="AF15" s="27"/>
+      <c r="AC15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="AD15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="AE15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="AF15" s="27">
+        <v>2.6</v>
+      </c>
     </row>
     <row r="16" spans="2:32" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="25" t="s">
@@ -11936,10 +12008,18 @@
       <c r="AB16" s="27">
         <v>13</v>
       </c>
-      <c r="AC16" s="27"/>
-      <c r="AD16" s="27"/>
-      <c r="AE16" s="27"/>
-      <c r="AF16" s="27"/>
+      <c r="AC16" s="27">
+        <v>13</v>
+      </c>
+      <c r="AD16" s="27">
+        <v>13</v>
+      </c>
+      <c r="AE16" s="27">
+        <v>13</v>
+      </c>
+      <c r="AF16" s="27">
+        <v>13</v>
+      </c>
     </row>
     <row r="17" spans="2:32" ht="14" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B17" s="28" t="s">
@@ -12023,10 +12103,18 @@
       <c r="AB17" s="23">
         <v>1331</v>
       </c>
-      <c r="AC17" s="23"/>
-      <c r="AD17" s="23"/>
-      <c r="AE17" s="23"/>
-      <c r="AF17" s="23"/>
+      <c r="AC17" s="23">
+        <v>1340</v>
+      </c>
+      <c r="AD17" s="23">
+        <v>1336</v>
+      </c>
+      <c r="AE17" s="23">
+        <v>1344</v>
+      </c>
+      <c r="AF17" s="23">
+        <v>1340</v>
+      </c>
     </row>
     <row r="18" spans="2:32" ht="14" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B18" s="29" t="s">
@@ -12107,11 +12195,21 @@
       <c r="AA18" s="30">
         <v>4725</v>
       </c>
-      <c r="AB18" s="30"/>
-      <c r="AC18" s="30"/>
-      <c r="AD18" s="30"/>
-      <c r="AE18" s="30"/>
-      <c r="AF18" s="30"/>
+      <c r="AB18" s="30">
+        <v>4552</v>
+      </c>
+      <c r="AC18" s="30">
+        <v>2838</v>
+      </c>
+      <c r="AD18" s="30">
+        <v>4567</v>
+      </c>
+      <c r="AE18" s="30">
+        <v>7006</v>
+      </c>
+      <c r="AF18" s="30">
+        <v>1777</v>
+      </c>
     </row>
     <row r="19" spans="2:32" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" s="37" t="s">
@@ -12237,4 +12335,2700 @@
   <pageMargins left="0" right="0" top="0.74803149606299213" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="83" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{045B879F-0CD4-4938-9579-2563F94D1C0E}">
+  <dimension ref="B1:AG35"/>
+  <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="13.5" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="2.25" style="2" customWidth="1"/>
+    <col min="2" max="2" width="24.08203125" style="2" customWidth="1"/>
+    <col min="3" max="33" width="4.25" style="2" customWidth="1"/>
+    <col min="34" max="16384" width="8.58203125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" s="20"/>
+    </row>
+    <row r="2" spans="2:33" ht="15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" s="19"/>
+    </row>
+    <row r="4" spans="2:33" ht="15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" s="3">
+        <v>45839</v>
+      </c>
+      <c r="C4" s="4">
+        <f>$B$4+C$6-1</f>
+        <v>45839</v>
+      </c>
+      <c r="D4" s="4">
+        <f t="shared" ref="D4:AG4" si="0">$B$4+D$6-1</f>
+        <v>45840</v>
+      </c>
+      <c r="E4" s="4">
+        <f t="shared" si="0"/>
+        <v>45841</v>
+      </c>
+      <c r="F4" s="4">
+        <f t="shared" si="0"/>
+        <v>45842</v>
+      </c>
+      <c r="G4" s="4">
+        <f t="shared" si="0"/>
+        <v>45843</v>
+      </c>
+      <c r="H4" s="4">
+        <f t="shared" si="0"/>
+        <v>45844</v>
+      </c>
+      <c r="I4" s="4">
+        <f t="shared" si="0"/>
+        <v>45845</v>
+      </c>
+      <c r="J4" s="4">
+        <f t="shared" si="0"/>
+        <v>45846</v>
+      </c>
+      <c r="K4" s="4">
+        <f t="shared" si="0"/>
+        <v>45847</v>
+      </c>
+      <c r="L4" s="4">
+        <f t="shared" si="0"/>
+        <v>45848</v>
+      </c>
+      <c r="M4" s="4">
+        <f t="shared" si="0"/>
+        <v>45849</v>
+      </c>
+      <c r="N4" s="4">
+        <f t="shared" si="0"/>
+        <v>45850</v>
+      </c>
+      <c r="O4" s="4">
+        <f t="shared" si="0"/>
+        <v>45851</v>
+      </c>
+      <c r="P4" s="4">
+        <f t="shared" si="0"/>
+        <v>45852</v>
+      </c>
+      <c r="Q4" s="4">
+        <f t="shared" si="0"/>
+        <v>45853</v>
+      </c>
+      <c r="R4" s="4">
+        <f>$B$4+R$6-1</f>
+        <v>45854</v>
+      </c>
+      <c r="S4" s="4">
+        <f t="shared" si="0"/>
+        <v>45855</v>
+      </c>
+      <c r="T4" s="4">
+        <f t="shared" si="0"/>
+        <v>45856</v>
+      </c>
+      <c r="U4" s="4">
+        <f t="shared" si="0"/>
+        <v>45857</v>
+      </c>
+      <c r="V4" s="4">
+        <f t="shared" si="0"/>
+        <v>45858</v>
+      </c>
+      <c r="W4" s="4">
+        <f t="shared" si="0"/>
+        <v>45859</v>
+      </c>
+      <c r="X4" s="4">
+        <f t="shared" si="0"/>
+        <v>45860</v>
+      </c>
+      <c r="Y4" s="4">
+        <f t="shared" si="0"/>
+        <v>45861</v>
+      </c>
+      <c r="Z4" s="4">
+        <f t="shared" si="0"/>
+        <v>45862</v>
+      </c>
+      <c r="AA4" s="4">
+        <f t="shared" si="0"/>
+        <v>45863</v>
+      </c>
+      <c r="AB4" s="4">
+        <f t="shared" si="0"/>
+        <v>45864</v>
+      </c>
+      <c r="AC4" s="4">
+        <f t="shared" si="0"/>
+        <v>45865</v>
+      </c>
+      <c r="AD4" s="4">
+        <f t="shared" si="0"/>
+        <v>45866</v>
+      </c>
+      <c r="AE4" s="4">
+        <f t="shared" si="0"/>
+        <v>45867</v>
+      </c>
+      <c r="AF4" s="4">
+        <f t="shared" si="0"/>
+        <v>45868</v>
+      </c>
+      <c r="AG4" s="4">
+        <f t="shared" si="0"/>
+        <v>45869</v>
+      </c>
+    </row>
+    <row r="5" spans="2:33" ht="14" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="C5" s="32" t="str">
+        <f>TEXT(C$4,"aaa")</f>
+        <v>火</v>
+      </c>
+      <c r="D5" s="32" t="str">
+        <f t="shared" ref="D5:AG5" si="1">TEXT(D$4,"aaa")</f>
+        <v>水</v>
+      </c>
+      <c r="E5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>木</v>
+      </c>
+      <c r="F5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>金</v>
+      </c>
+      <c r="G5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>土</v>
+      </c>
+      <c r="H5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>日</v>
+      </c>
+      <c r="I5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>月</v>
+      </c>
+      <c r="J5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>火</v>
+      </c>
+      <c r="K5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>水</v>
+      </c>
+      <c r="L5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>木</v>
+      </c>
+      <c r="M5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>金</v>
+      </c>
+      <c r="N5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>土</v>
+      </c>
+      <c r="O5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>日</v>
+      </c>
+      <c r="P5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>月</v>
+      </c>
+      <c r="Q5" s="32" t="str">
+        <f>TEXT(Q$4,"aaa")</f>
+        <v>火</v>
+      </c>
+      <c r="R5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>水</v>
+      </c>
+      <c r="S5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>木</v>
+      </c>
+      <c r="T5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>金</v>
+      </c>
+      <c r="U5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>土</v>
+      </c>
+      <c r="V5" s="32" t="str">
+        <f>TEXT(V$4,"aaa")</f>
+        <v>日</v>
+      </c>
+      <c r="W5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>月</v>
+      </c>
+      <c r="X5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>火</v>
+      </c>
+      <c r="Y5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>水</v>
+      </c>
+      <c r="Z5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>木</v>
+      </c>
+      <c r="AA5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>金</v>
+      </c>
+      <c r="AB5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>土</v>
+      </c>
+      <c r="AC5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>日</v>
+      </c>
+      <c r="AD5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>月</v>
+      </c>
+      <c r="AE5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>火</v>
+      </c>
+      <c r="AF5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>水</v>
+      </c>
+      <c r="AG5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>木</v>
+      </c>
+    </row>
+    <row r="6" spans="2:33" ht="14" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B6" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="43">
+        <v>1</v>
+      </c>
+      <c r="D6" s="43">
+        <f>C6+1</f>
+        <v>2</v>
+      </c>
+      <c r="E6" s="43">
+        <f t="shared" ref="E6:AG6" si="2">D6+1</f>
+        <v>3</v>
+      </c>
+      <c r="F6" s="43">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="43">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="H6" s="43">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="I6" s="43">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="J6" s="43">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="K6" s="43">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="L6" s="43">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M6" s="43">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="N6" s="43">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="O6" s="43">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="P6" s="43">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="Q6" s="43">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="R6" s="43">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="S6" s="43">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="T6" s="43">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="U6" s="43">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="V6" s="43">
+        <f>U6+1</f>
+        <v>20</v>
+      </c>
+      <c r="W6" s="43">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+      <c r="X6" s="43">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+      <c r="Y6" s="43">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="Z6" s="43">
+        <f t="shared" si="2"/>
+        <v>24</v>
+      </c>
+      <c r="AA6" s="43">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="AB6" s="43">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="AC6" s="33">
+        <f t="shared" si="2"/>
+        <v>27</v>
+      </c>
+      <c r="AD6" s="33">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+      <c r="AE6" s="33">
+        <f t="shared" si="2"/>
+        <v>29</v>
+      </c>
+      <c r="AF6" s="33">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="AG6" s="33">
+        <f t="shared" si="2"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="14">
+        <v>101</v>
+      </c>
+      <c r="D7" s="13">
+        <v>104</v>
+      </c>
+      <c r="E7" s="13">
+        <v>105</v>
+      </c>
+      <c r="F7" s="47">
+        <v>99</v>
+      </c>
+      <c r="G7" s="13">
+        <v>105</v>
+      </c>
+      <c r="H7" s="13">
+        <v>106</v>
+      </c>
+      <c r="I7" s="13">
+        <v>111</v>
+      </c>
+      <c r="J7" s="47">
+        <v>95</v>
+      </c>
+      <c r="K7" s="47">
+        <v>93</v>
+      </c>
+      <c r="L7" s="13">
+        <v>100</v>
+      </c>
+      <c r="M7" s="13">
+        <v>119</v>
+      </c>
+      <c r="N7" s="13">
+        <v>105</v>
+      </c>
+      <c r="O7" s="13">
+        <v>108</v>
+      </c>
+      <c r="P7" s="13">
+        <v>106</v>
+      </c>
+      <c r="Q7" s="13">
+        <v>110</v>
+      </c>
+      <c r="R7" s="13">
+        <v>114</v>
+      </c>
+      <c r="S7" s="13">
+        <v>102</v>
+      </c>
+      <c r="T7" s="13">
+        <v>112</v>
+      </c>
+      <c r="U7" s="13">
+        <v>120</v>
+      </c>
+      <c r="V7" s="13">
+        <v>107</v>
+      </c>
+      <c r="W7" s="13">
+        <v>110</v>
+      </c>
+      <c r="X7" s="13">
+        <v>103</v>
+      </c>
+      <c r="Y7" s="13">
+        <v>102</v>
+      </c>
+      <c r="Z7" s="13">
+        <v>119</v>
+      </c>
+      <c r="AA7" s="13">
+        <v>107</v>
+      </c>
+      <c r="AB7" s="14">
+        <v>106</v>
+      </c>
+      <c r="AC7" s="13">
+        <v>103</v>
+      </c>
+      <c r="AD7" s="13">
+        <v>109</v>
+      </c>
+      <c r="AE7" s="13">
+        <v>109</v>
+      </c>
+      <c r="AF7" s="13">
+        <v>104</v>
+      </c>
+      <c r="AG7" s="13">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="13">
+        <v>60</v>
+      </c>
+      <c r="D8" s="13">
+        <v>63</v>
+      </c>
+      <c r="E8" s="13">
+        <v>63</v>
+      </c>
+      <c r="F8" s="47">
+        <v>59</v>
+      </c>
+      <c r="G8" s="13">
+        <v>64</v>
+      </c>
+      <c r="H8" s="13">
+        <v>63</v>
+      </c>
+      <c r="I8" s="13">
+        <v>62</v>
+      </c>
+      <c r="J8" s="13">
+        <v>64</v>
+      </c>
+      <c r="K8" s="13">
+        <v>59</v>
+      </c>
+      <c r="L8" s="13">
+        <v>62</v>
+      </c>
+      <c r="M8" s="13">
+        <v>65</v>
+      </c>
+      <c r="N8" s="13">
+        <v>61</v>
+      </c>
+      <c r="O8" s="13">
+        <v>65</v>
+      </c>
+      <c r="P8" s="47">
+        <v>59</v>
+      </c>
+      <c r="Q8" s="13">
+        <v>69</v>
+      </c>
+      <c r="R8" s="13">
+        <v>66</v>
+      </c>
+      <c r="S8" s="13">
+        <v>65</v>
+      </c>
+      <c r="T8" s="13">
+        <v>62</v>
+      </c>
+      <c r="U8" s="13">
+        <v>60</v>
+      </c>
+      <c r="V8" s="13">
+        <v>63</v>
+      </c>
+      <c r="W8" s="13">
+        <v>65</v>
+      </c>
+      <c r="X8" s="13">
+        <v>63</v>
+      </c>
+      <c r="Y8" s="13">
+        <v>62</v>
+      </c>
+      <c r="Z8" s="13">
+        <v>72</v>
+      </c>
+      <c r="AA8" s="13">
+        <v>63</v>
+      </c>
+      <c r="AB8" s="13">
+        <v>61</v>
+      </c>
+      <c r="AC8" s="13">
+        <v>60</v>
+      </c>
+      <c r="AD8" s="13">
+        <v>68</v>
+      </c>
+      <c r="AE8" s="13">
+        <v>62</v>
+      </c>
+      <c r="AF8" s="13">
+        <v>65</v>
+      </c>
+      <c r="AG8" s="13">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="9">
+        <v>36.5</v>
+      </c>
+      <c r="D9" s="9">
+        <v>36.5</v>
+      </c>
+      <c r="E9" s="9">
+        <v>36.5</v>
+      </c>
+      <c r="F9" s="9">
+        <v>36.6</v>
+      </c>
+      <c r="G9" s="9">
+        <v>36.5</v>
+      </c>
+      <c r="H9" s="9">
+        <v>36.6</v>
+      </c>
+      <c r="I9" s="9">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="J9" s="9">
+        <v>36.6</v>
+      </c>
+      <c r="K9" s="9">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="L9" s="9">
+        <v>36.5</v>
+      </c>
+      <c r="M9" s="9">
+        <v>36.6</v>
+      </c>
+      <c r="N9" s="9">
+        <v>36.4</v>
+      </c>
+      <c r="O9" s="9">
+        <v>36.5</v>
+      </c>
+      <c r="P9" s="9">
+        <v>36.6</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>36.4</v>
+      </c>
+      <c r="R9" s="9">
+        <v>36.4</v>
+      </c>
+      <c r="S9" s="9">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="T9" s="9">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="U9" s="9">
+        <v>36.6</v>
+      </c>
+      <c r="V9" s="9">
+        <v>36.6</v>
+      </c>
+      <c r="W9" s="9">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="X9" s="9">
+        <v>36.6</v>
+      </c>
+      <c r="Y9" s="9">
+        <v>36.4</v>
+      </c>
+      <c r="Z9" s="9">
+        <v>36.9</v>
+      </c>
+      <c r="AA9" s="9">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="AB9" s="9">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="AC9" s="9">
+        <v>36.6</v>
+      </c>
+      <c r="AD9" s="9">
+        <v>36.6</v>
+      </c>
+      <c r="AE9" s="9">
+        <v>36.5</v>
+      </c>
+      <c r="AF9" s="9">
+        <v>36.5</v>
+      </c>
+      <c r="AG9" s="9">
+        <v>36.5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="10">
+        <v>98</v>
+      </c>
+      <c r="D10" s="10">
+        <v>99</v>
+      </c>
+      <c r="E10" s="10">
+        <v>97</v>
+      </c>
+      <c r="F10" s="10">
+        <v>98</v>
+      </c>
+      <c r="G10" s="10">
+        <v>97</v>
+      </c>
+      <c r="H10" s="10">
+        <v>97</v>
+      </c>
+      <c r="I10" s="10">
+        <v>97</v>
+      </c>
+      <c r="J10" s="10">
+        <v>95</v>
+      </c>
+      <c r="K10" s="10">
+        <v>96</v>
+      </c>
+      <c r="L10" s="10">
+        <v>96</v>
+      </c>
+      <c r="M10" s="10">
+        <v>98</v>
+      </c>
+      <c r="N10" s="10">
+        <v>97</v>
+      </c>
+      <c r="O10" s="10">
+        <v>95</v>
+      </c>
+      <c r="P10" s="10">
+        <v>98</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>97</v>
+      </c>
+      <c r="R10" s="10">
+        <v>99</v>
+      </c>
+      <c r="S10" s="10">
+        <v>98</v>
+      </c>
+      <c r="T10" s="10">
+        <v>97</v>
+      </c>
+      <c r="U10" s="10">
+        <v>98</v>
+      </c>
+      <c r="V10" s="10">
+        <v>97</v>
+      </c>
+      <c r="W10" s="10">
+        <v>96</v>
+      </c>
+      <c r="X10" s="10">
+        <v>96</v>
+      </c>
+      <c r="Y10" s="10">
+        <v>95</v>
+      </c>
+      <c r="Z10" s="10">
+        <v>96</v>
+      </c>
+      <c r="AA10" s="10">
+        <v>98</v>
+      </c>
+      <c r="AB10" s="10">
+        <v>99</v>
+      </c>
+      <c r="AC10" s="10">
+        <v>98</v>
+      </c>
+      <c r="AD10" s="10">
+        <v>97</v>
+      </c>
+      <c r="AE10" s="10">
+        <v>98</v>
+      </c>
+      <c r="AF10" s="10">
+        <v>98</v>
+      </c>
+      <c r="AG10" s="10">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="2:33" ht="14" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B11" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="11">
+        <v>67</v>
+      </c>
+      <c r="D11" s="11">
+        <v>66</v>
+      </c>
+      <c r="E11" s="11">
+        <v>67</v>
+      </c>
+      <c r="F11" s="11">
+        <v>68</v>
+      </c>
+      <c r="G11" s="11">
+        <v>68</v>
+      </c>
+      <c r="H11" s="11">
+        <v>78</v>
+      </c>
+      <c r="I11" s="11">
+        <v>66</v>
+      </c>
+      <c r="J11" s="12">
+        <v>70</v>
+      </c>
+      <c r="K11" s="11">
+        <v>69</v>
+      </c>
+      <c r="L11" s="11">
+        <v>66</v>
+      </c>
+      <c r="M11" s="11">
+        <v>71</v>
+      </c>
+      <c r="N11" s="11">
+        <v>69</v>
+      </c>
+      <c r="O11" s="11">
+        <v>67</v>
+      </c>
+      <c r="P11" s="11">
+        <v>63</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>68</v>
+      </c>
+      <c r="R11" s="12">
+        <v>73</v>
+      </c>
+      <c r="S11" s="11">
+        <v>67</v>
+      </c>
+      <c r="T11" s="11">
+        <v>67</v>
+      </c>
+      <c r="U11" s="11">
+        <v>65</v>
+      </c>
+      <c r="V11" s="11">
+        <v>70</v>
+      </c>
+      <c r="W11" s="11">
+        <v>65</v>
+      </c>
+      <c r="X11" s="11">
+        <v>62</v>
+      </c>
+      <c r="Y11" s="11">
+        <v>68</v>
+      </c>
+      <c r="Z11" s="11">
+        <v>72</v>
+      </c>
+      <c r="AA11" s="11">
+        <v>66</v>
+      </c>
+      <c r="AB11" s="12">
+        <v>67</v>
+      </c>
+      <c r="AC11" s="11">
+        <v>64</v>
+      </c>
+      <c r="AD11" s="11">
+        <v>67</v>
+      </c>
+      <c r="AE11" s="11">
+        <v>69</v>
+      </c>
+      <c r="AF11" s="11">
+        <v>71</v>
+      </c>
+      <c r="AG11" s="11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="26">
+        <v>63.8</v>
+      </c>
+      <c r="D12" s="26">
+        <v>64.2</v>
+      </c>
+      <c r="E12" s="26">
+        <v>64.05</v>
+      </c>
+      <c r="F12" s="26">
+        <v>64.099999999999994</v>
+      </c>
+      <c r="G12" s="26">
+        <v>63.75</v>
+      </c>
+      <c r="H12" s="26">
+        <v>64.400000000000006</v>
+      </c>
+      <c r="I12" s="26">
+        <v>63.9</v>
+      </c>
+      <c r="J12" s="26">
+        <v>63.85</v>
+      </c>
+      <c r="K12" s="26">
+        <v>63.5</v>
+      </c>
+      <c r="L12" s="26">
+        <v>63.75</v>
+      </c>
+      <c r="M12" s="26">
+        <v>63.8</v>
+      </c>
+      <c r="N12" s="26">
+        <v>63.65</v>
+      </c>
+      <c r="O12" s="26">
+        <v>63.9</v>
+      </c>
+      <c r="P12" s="26">
+        <v>64.45</v>
+      </c>
+      <c r="Q12" s="26">
+        <v>63.95</v>
+      </c>
+      <c r="R12" s="26">
+        <v>63.9</v>
+      </c>
+      <c r="S12" s="26">
+        <v>64.400000000000006</v>
+      </c>
+      <c r="T12" s="26">
+        <v>64.900000000000006</v>
+      </c>
+      <c r="U12" s="26">
+        <v>64.55</v>
+      </c>
+      <c r="V12" s="26">
+        <v>64.900000000000006</v>
+      </c>
+      <c r="W12" s="26">
+        <v>64.900000000000006</v>
+      </c>
+      <c r="X12" s="26">
+        <v>64.900000000000006</v>
+      </c>
+      <c r="Y12" s="26">
+        <v>64.8</v>
+      </c>
+      <c r="Z12" s="26">
+        <v>64.95</v>
+      </c>
+      <c r="AA12" s="26">
+        <v>64.95</v>
+      </c>
+      <c r="AB12" s="26">
+        <v>64.95</v>
+      </c>
+      <c r="AC12" s="26">
+        <v>65.400000000000006</v>
+      </c>
+      <c r="AD12" s="26">
+        <v>64.650000000000006</v>
+      </c>
+      <c r="AE12" s="26">
+        <v>64.75</v>
+      </c>
+      <c r="AF12" s="26">
+        <v>65</v>
+      </c>
+      <c r="AG12" s="26">
+        <v>65.05</v>
+      </c>
+    </row>
+    <row r="13" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="27">
+        <v>22.4</v>
+      </c>
+      <c r="D13" s="27">
+        <v>22.6</v>
+      </c>
+      <c r="E13" s="27">
+        <v>22.4</v>
+      </c>
+      <c r="F13" s="27">
+        <v>22.9</v>
+      </c>
+      <c r="G13" s="27">
+        <v>22.1</v>
+      </c>
+      <c r="H13" s="27">
+        <v>23.3</v>
+      </c>
+      <c r="I13" s="27">
+        <v>22.9</v>
+      </c>
+      <c r="J13" s="27">
+        <v>22.3</v>
+      </c>
+      <c r="K13" s="27">
+        <v>22.5</v>
+      </c>
+      <c r="L13" s="27">
+        <v>22.7</v>
+      </c>
+      <c r="M13" s="27">
+        <v>22.7</v>
+      </c>
+      <c r="N13" s="27">
+        <v>23</v>
+      </c>
+      <c r="O13" s="27">
+        <v>22.6</v>
+      </c>
+      <c r="P13" s="27">
+        <v>22.5</v>
+      </c>
+      <c r="Q13" s="27">
+        <v>22.7</v>
+      </c>
+      <c r="R13" s="27">
+        <v>22.5</v>
+      </c>
+      <c r="S13" s="27">
+        <v>22.6</v>
+      </c>
+      <c r="T13" s="27">
+        <v>22.7</v>
+      </c>
+      <c r="U13" s="27">
+        <v>22</v>
+      </c>
+      <c r="V13" s="27">
+        <v>22.5</v>
+      </c>
+      <c r="W13" s="27">
+        <v>22.8</v>
+      </c>
+      <c r="X13" s="27">
+        <v>23</v>
+      </c>
+      <c r="Y13" s="27">
+        <v>23.2</v>
+      </c>
+      <c r="Z13" s="27">
+        <v>23</v>
+      </c>
+      <c r="AA13" s="27">
+        <v>22.8</v>
+      </c>
+      <c r="AB13" s="27">
+        <v>22.4</v>
+      </c>
+      <c r="AC13" s="27">
+        <v>22.9</v>
+      </c>
+      <c r="AD13" s="27">
+        <v>23.2</v>
+      </c>
+      <c r="AE13" s="27">
+        <v>22.7</v>
+      </c>
+      <c r="AF13" s="27">
+        <v>23.2</v>
+      </c>
+      <c r="AG13" s="27">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="27">
+        <v>47.15</v>
+      </c>
+      <c r="D14" s="27">
+        <v>47.35</v>
+      </c>
+      <c r="E14" s="27">
+        <v>47.35</v>
+      </c>
+      <c r="F14" s="27">
+        <v>47.05</v>
+      </c>
+      <c r="G14" s="27">
+        <v>47.25</v>
+      </c>
+      <c r="H14" s="27">
+        <v>46.8</v>
+      </c>
+      <c r="I14" s="27">
+        <v>46.9</v>
+      </c>
+      <c r="J14" s="27">
+        <v>47.25</v>
+      </c>
+      <c r="K14" s="27">
+        <v>46.9</v>
+      </c>
+      <c r="L14" s="27">
+        <v>46.9</v>
+      </c>
+      <c r="M14" s="27">
+        <v>47</v>
+      </c>
+      <c r="N14" s="27">
+        <v>46.65</v>
+      </c>
+      <c r="O14" s="27">
+        <v>47.1</v>
+      </c>
+      <c r="P14" s="27">
+        <v>47.55</v>
+      </c>
+      <c r="Q14" s="27">
+        <v>47.1</v>
+      </c>
+      <c r="R14" s="27">
+        <v>47.2</v>
+      </c>
+      <c r="S14" s="27">
+        <v>47.9</v>
+      </c>
+      <c r="T14" s="27">
+        <v>47.8</v>
+      </c>
+      <c r="U14" s="27">
+        <v>47.35</v>
+      </c>
+      <c r="V14" s="27">
+        <v>47.9</v>
+      </c>
+      <c r="W14" s="27">
+        <v>47.75</v>
+      </c>
+      <c r="X14" s="27">
+        <v>47.55</v>
+      </c>
+      <c r="Y14" s="27">
+        <v>47.4</v>
+      </c>
+      <c r="Z14" s="27">
+        <v>47.6</v>
+      </c>
+      <c r="AA14" s="27">
+        <v>47.75</v>
+      </c>
+      <c r="AB14" s="27">
+        <v>47.95</v>
+      </c>
+      <c r="AC14" s="27">
+        <v>48.05</v>
+      </c>
+      <c r="AD14" s="27">
+        <v>47.3</v>
+      </c>
+      <c r="AE14" s="27">
+        <v>47.65</v>
+      </c>
+      <c r="AF14" s="27">
+        <v>47.5</v>
+      </c>
+      <c r="AG14" s="27">
+        <v>47.65</v>
+      </c>
+    </row>
+    <row r="15" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="D15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="E15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="F15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="G15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="H15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="I15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="J15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="K15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="L15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="M15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="N15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="O15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="P15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="Q15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="R15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="S15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="T15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="U15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="V15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="W15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="X15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="Y15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="Z15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="AA15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="AB15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="AC15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="AD15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="AE15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="AF15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="AG15" s="27">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="16" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="27">
+        <v>13</v>
+      </c>
+      <c r="D16" s="27">
+        <v>13</v>
+      </c>
+      <c r="E16" s="27">
+        <v>13</v>
+      </c>
+      <c r="F16" s="27">
+        <v>13</v>
+      </c>
+      <c r="G16" s="27">
+        <v>13</v>
+      </c>
+      <c r="H16" s="27">
+        <v>13</v>
+      </c>
+      <c r="I16" s="27">
+        <v>13</v>
+      </c>
+      <c r="J16" s="27">
+        <v>13</v>
+      </c>
+      <c r="K16" s="27">
+        <v>13</v>
+      </c>
+      <c r="L16" s="27">
+        <v>13</v>
+      </c>
+      <c r="M16" s="27">
+        <v>13</v>
+      </c>
+      <c r="N16" s="27">
+        <v>13</v>
+      </c>
+      <c r="O16" s="27">
+        <v>13</v>
+      </c>
+      <c r="P16" s="27">
+        <v>13</v>
+      </c>
+      <c r="Q16" s="27">
+        <v>13</v>
+      </c>
+      <c r="R16" s="27">
+        <v>13</v>
+      </c>
+      <c r="S16" s="27">
+        <v>13</v>
+      </c>
+      <c r="T16" s="27">
+        <v>13</v>
+      </c>
+      <c r="U16" s="27">
+        <v>13</v>
+      </c>
+      <c r="V16" s="27">
+        <v>13</v>
+      </c>
+      <c r="W16" s="27">
+        <v>13</v>
+      </c>
+      <c r="X16" s="27">
+        <v>13.5</v>
+      </c>
+      <c r="Y16" s="27">
+        <v>13.5</v>
+      </c>
+      <c r="Z16" s="27">
+        <v>13.5</v>
+      </c>
+      <c r="AA16" s="27">
+        <v>13.5</v>
+      </c>
+      <c r="AB16" s="27">
+        <v>13</v>
+      </c>
+      <c r="AC16" s="27">
+        <v>13.5</v>
+      </c>
+      <c r="AD16" s="27">
+        <v>13.5</v>
+      </c>
+      <c r="AE16" s="27">
+        <v>13</v>
+      </c>
+      <c r="AF16" s="27">
+        <v>13.5</v>
+      </c>
+      <c r="AG16" s="27">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:33" ht="14" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B17" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="23">
+        <v>1342</v>
+      </c>
+      <c r="D17" s="23">
+        <v>1348</v>
+      </c>
+      <c r="E17" s="23">
+        <v>1348</v>
+      </c>
+      <c r="F17" s="23">
+        <v>1340</v>
+      </c>
+      <c r="G17" s="23">
+        <v>1345</v>
+      </c>
+      <c r="H17" s="23">
+        <v>1333</v>
+      </c>
+      <c r="I17" s="23">
+        <v>1336</v>
+      </c>
+      <c r="J17" s="23">
+        <v>1345</v>
+      </c>
+      <c r="K17" s="23">
+        <v>1334</v>
+      </c>
+      <c r="L17" s="23">
+        <v>1335</v>
+      </c>
+      <c r="M17" s="23">
+        <v>1337</v>
+      </c>
+      <c r="N17" s="23">
+        <v>1328</v>
+      </c>
+      <c r="O17" s="23">
+        <v>1341</v>
+      </c>
+      <c r="P17" s="23">
+        <v>1355</v>
+      </c>
+      <c r="Q17" s="23">
+        <v>1341</v>
+      </c>
+      <c r="R17" s="23">
+        <v>1343</v>
+      </c>
+      <c r="S17" s="23">
+        <v>1347</v>
+      </c>
+      <c r="T17" s="23">
+        <v>1362</v>
+      </c>
+      <c r="U17" s="23">
+        <v>1349</v>
+      </c>
+      <c r="V17" s="23">
+        <v>1366</v>
+      </c>
+      <c r="W17" s="23">
+        <v>1361</v>
+      </c>
+      <c r="X17" s="23">
+        <v>1355</v>
+      </c>
+      <c r="Y17" s="23">
+        <v>1351</v>
+      </c>
+      <c r="Z17" s="23">
+        <v>1358</v>
+      </c>
+      <c r="AA17" s="23">
+        <v>1360</v>
+      </c>
+      <c r="AB17" s="23">
+        <v>1367</v>
+      </c>
+      <c r="AC17" s="23">
+        <v>1370</v>
+      </c>
+      <c r="AD17" s="23">
+        <v>1348</v>
+      </c>
+      <c r="AE17" s="23">
+        <v>1359</v>
+      </c>
+      <c r="AF17" s="23">
+        <v>1355</v>
+      </c>
+      <c r="AG17" s="23">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="18" spans="2:33" ht="14" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B18" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="30">
+        <v>4686</v>
+      </c>
+      <c r="D18" s="30">
+        <v>6321</v>
+      </c>
+      <c r="E18" s="30">
+        <v>4649</v>
+      </c>
+      <c r="F18" s="30">
+        <v>4737</v>
+      </c>
+      <c r="G18" s="30">
+        <v>1755</v>
+      </c>
+      <c r="H18" s="30">
+        <v>7689</v>
+      </c>
+      <c r="I18" s="30">
+        <v>4540</v>
+      </c>
+      <c r="J18" s="30">
+        <v>5056</v>
+      </c>
+      <c r="K18" s="30">
+        <v>4465</v>
+      </c>
+      <c r="L18" s="30">
+        <v>5895</v>
+      </c>
+      <c r="M18" s="30">
+        <v>2435</v>
+      </c>
+      <c r="N18" s="30">
+        <v>55</v>
+      </c>
+      <c r="O18" s="30">
+        <v>5014</v>
+      </c>
+      <c r="P18" s="30">
+        <v>5099</v>
+      </c>
+      <c r="Q18" s="30">
+        <v>4692</v>
+      </c>
+      <c r="R18" s="30">
+        <v>2203</v>
+      </c>
+      <c r="S18" s="30">
+        <v>4959</v>
+      </c>
+      <c r="T18" s="30">
+        <v>4606</v>
+      </c>
+      <c r="U18" s="30">
+        <v>4831</v>
+      </c>
+      <c r="V18" s="30">
+        <v>6613</v>
+      </c>
+      <c r="W18" s="30">
+        <v>4964</v>
+      </c>
+      <c r="X18" s="30">
+        <v>3099</v>
+      </c>
+      <c r="Y18" s="30">
+        <v>4586</v>
+      </c>
+      <c r="Z18" s="30">
+        <v>4621</v>
+      </c>
+      <c r="AA18" s="30">
+        <v>5116</v>
+      </c>
+      <c r="AB18" s="30">
+        <v>4413</v>
+      </c>
+      <c r="AC18" s="30">
+        <v>4618</v>
+      </c>
+      <c r="AD18" s="30">
+        <v>4562</v>
+      </c>
+      <c r="AE18" s="30">
+        <v>4595</v>
+      </c>
+      <c r="AF18" s="30">
+        <v>2694</v>
+      </c>
+      <c r="AG18" s="30">
+        <v>5335</v>
+      </c>
+    </row>
+    <row r="19" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
+      <c r="L19" s="39"/>
+      <c r="M19" s="39"/>
+      <c r="N19" s="39"/>
+      <c r="O19" s="39"/>
+      <c r="P19" s="40"/>
+      <c r="Q19" s="39"/>
+      <c r="R19" s="39"/>
+      <c r="S19" s="32"/>
+      <c r="T19" s="32"/>
+      <c r="U19" s="32"/>
+      <c r="V19" s="32"/>
+      <c r="W19" s="32"/>
+      <c r="X19" s="32"/>
+      <c r="Y19" s="32"/>
+      <c r="Z19" s="40"/>
+      <c r="AA19" s="32"/>
+      <c r="AB19" s="32"/>
+      <c r="AC19" s="32"/>
+      <c r="AD19" s="40"/>
+      <c r="AE19" s="40"/>
+      <c r="AF19" s="32"/>
+      <c r="AG19" s="32"/>
+    </row>
+    <row r="20" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" s="34"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="39"/>
+      <c r="L20" s="39"/>
+      <c r="M20" s="39"/>
+      <c r="N20" s="39"/>
+      <c r="O20" s="39"/>
+      <c r="P20" s="40"/>
+      <c r="Q20" s="39"/>
+      <c r="R20" s="39"/>
+      <c r="S20" s="32"/>
+      <c r="T20" s="32"/>
+      <c r="U20" s="32"/>
+      <c r="V20" s="39"/>
+      <c r="W20" s="32"/>
+      <c r="X20" s="39"/>
+      <c r="Y20" s="32"/>
+      <c r="Z20" s="40"/>
+      <c r="AA20" s="32"/>
+      <c r="AB20" s="32"/>
+      <c r="AC20" s="32"/>
+      <c r="AD20" s="40"/>
+      <c r="AE20" s="32"/>
+      <c r="AF20" s="32"/>
+      <c r="AG20" s="32"/>
+    </row>
+    <row r="21" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" s="32"/>
+    </row>
+    <row r="22" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" s="34" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" s="31" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24" s="35" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25" s="35"/>
+    </row>
+    <row r="26" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B26" s="42" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B27" s="50"/>
+    </row>
+    <row r="28" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B28" s="50"/>
+    </row>
+    <row r="29" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29" s="50"/>
+    </row>
+    <row r="30" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B30" s="49"/>
+    </row>
+    <row r="31" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B31" s="49"/>
+    </row>
+    <row r="32" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B32" s="49"/>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B33" s="49"/>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B34" s="51"/>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B35" s="51"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0" right="0" top="0.74803149606299213" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="83" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D87C1594-FFCF-4C59-A66A-145431DBDDB7}">
+  <dimension ref="B1:AG35"/>
+  <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="13.5" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="2.25" style="2" customWidth="1"/>
+    <col min="2" max="2" width="24.08203125" style="2" customWidth="1"/>
+    <col min="3" max="33" width="4.25" style="2" customWidth="1"/>
+    <col min="34" max="16384" width="8.58203125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" s="20"/>
+    </row>
+    <row r="2" spans="2:33" ht="15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" s="19"/>
+    </row>
+    <row r="4" spans="2:33" ht="15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" s="3">
+        <v>45870</v>
+      </c>
+      <c r="C4" s="4">
+        <f>$B$4+C$6-1</f>
+        <v>45870</v>
+      </c>
+      <c r="D4" s="4">
+        <f t="shared" ref="D4:AG4" si="0">$B$4+D$6-1</f>
+        <v>45871</v>
+      </c>
+      <c r="E4" s="4">
+        <f t="shared" si="0"/>
+        <v>45872</v>
+      </c>
+      <c r="F4" s="4">
+        <f t="shared" si="0"/>
+        <v>45873</v>
+      </c>
+      <c r="G4" s="4">
+        <f t="shared" si="0"/>
+        <v>45874</v>
+      </c>
+      <c r="H4" s="4">
+        <f t="shared" si="0"/>
+        <v>45875</v>
+      </c>
+      <c r="I4" s="4">
+        <f t="shared" si="0"/>
+        <v>45876</v>
+      </c>
+      <c r="J4" s="4">
+        <f t="shared" si="0"/>
+        <v>45877</v>
+      </c>
+      <c r="K4" s="4">
+        <f t="shared" si="0"/>
+        <v>45878</v>
+      </c>
+      <c r="L4" s="4">
+        <f t="shared" si="0"/>
+        <v>45879</v>
+      </c>
+      <c r="M4" s="4">
+        <f t="shared" si="0"/>
+        <v>45880</v>
+      </c>
+      <c r="N4" s="4">
+        <f t="shared" si="0"/>
+        <v>45881</v>
+      </c>
+      <c r="O4" s="4">
+        <f t="shared" si="0"/>
+        <v>45882</v>
+      </c>
+      <c r="P4" s="4">
+        <f t="shared" si="0"/>
+        <v>45883</v>
+      </c>
+      <c r="Q4" s="4">
+        <f t="shared" si="0"/>
+        <v>45884</v>
+      </c>
+      <c r="R4" s="4">
+        <f>$B$4+R$6-1</f>
+        <v>45885</v>
+      </c>
+      <c r="S4" s="4">
+        <f t="shared" si="0"/>
+        <v>45886</v>
+      </c>
+      <c r="T4" s="4">
+        <f t="shared" si="0"/>
+        <v>45887</v>
+      </c>
+      <c r="U4" s="4">
+        <f t="shared" si="0"/>
+        <v>45888</v>
+      </c>
+      <c r="V4" s="4">
+        <f t="shared" si="0"/>
+        <v>45889</v>
+      </c>
+      <c r="W4" s="4">
+        <f t="shared" si="0"/>
+        <v>45890</v>
+      </c>
+      <c r="X4" s="4">
+        <f t="shared" si="0"/>
+        <v>45891</v>
+      </c>
+      <c r="Y4" s="4">
+        <f t="shared" si="0"/>
+        <v>45892</v>
+      </c>
+      <c r="Z4" s="4">
+        <f t="shared" si="0"/>
+        <v>45893</v>
+      </c>
+      <c r="AA4" s="4">
+        <f t="shared" si="0"/>
+        <v>45894</v>
+      </c>
+      <c r="AB4" s="4">
+        <f t="shared" si="0"/>
+        <v>45895</v>
+      </c>
+      <c r="AC4" s="4">
+        <f t="shared" si="0"/>
+        <v>45896</v>
+      </c>
+      <c r="AD4" s="4">
+        <f t="shared" si="0"/>
+        <v>45897</v>
+      </c>
+      <c r="AE4" s="4">
+        <f t="shared" si="0"/>
+        <v>45898</v>
+      </c>
+      <c r="AF4" s="4">
+        <f t="shared" si="0"/>
+        <v>45899</v>
+      </c>
+      <c r="AG4" s="4">
+        <f t="shared" si="0"/>
+        <v>45900</v>
+      </c>
+    </row>
+    <row r="5" spans="2:33" ht="14" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="C5" s="32" t="str">
+        <f>TEXT(C$4,"aaa")</f>
+        <v>金</v>
+      </c>
+      <c r="D5" s="32" t="str">
+        <f t="shared" ref="D5:AG5" si="1">TEXT(D$4,"aaa")</f>
+        <v>土</v>
+      </c>
+      <c r="E5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>日</v>
+      </c>
+      <c r="F5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>月</v>
+      </c>
+      <c r="G5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>火</v>
+      </c>
+      <c r="H5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>水</v>
+      </c>
+      <c r="I5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>木</v>
+      </c>
+      <c r="J5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>金</v>
+      </c>
+      <c r="K5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>土</v>
+      </c>
+      <c r="L5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>日</v>
+      </c>
+      <c r="M5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>月</v>
+      </c>
+      <c r="N5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>火</v>
+      </c>
+      <c r="O5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>水</v>
+      </c>
+      <c r="P5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>木</v>
+      </c>
+      <c r="Q5" s="32" t="str">
+        <f>TEXT(Q$4,"aaa")</f>
+        <v>金</v>
+      </c>
+      <c r="R5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>土</v>
+      </c>
+      <c r="S5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>日</v>
+      </c>
+      <c r="T5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>月</v>
+      </c>
+      <c r="U5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>火</v>
+      </c>
+      <c r="V5" s="32" t="str">
+        <f>TEXT(V$4,"aaa")</f>
+        <v>水</v>
+      </c>
+      <c r="W5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>木</v>
+      </c>
+      <c r="X5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>金</v>
+      </c>
+      <c r="Y5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>土</v>
+      </c>
+      <c r="Z5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>日</v>
+      </c>
+      <c r="AA5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>月</v>
+      </c>
+      <c r="AB5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>火</v>
+      </c>
+      <c r="AC5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>水</v>
+      </c>
+      <c r="AD5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>木</v>
+      </c>
+      <c r="AE5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>金</v>
+      </c>
+      <c r="AF5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>土</v>
+      </c>
+      <c r="AG5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>日</v>
+      </c>
+    </row>
+    <row r="6" spans="2:33" ht="14" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B6" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="43">
+        <v>1</v>
+      </c>
+      <c r="D6" s="43">
+        <f>C6+1</f>
+        <v>2</v>
+      </c>
+      <c r="E6" s="43">
+        <f t="shared" ref="E6:AG6" si="2">D6+1</f>
+        <v>3</v>
+      </c>
+      <c r="F6" s="43">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="43">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="H6" s="43">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="I6" s="43">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="J6" s="43">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="K6" s="43">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="L6" s="43">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M6" s="43">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="N6" s="43">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="O6" s="43">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="P6" s="43">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="Q6" s="43">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="R6" s="43">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="S6" s="43">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="T6" s="43">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="U6" s="43">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="V6" s="43">
+        <f>U6+1</f>
+        <v>20</v>
+      </c>
+      <c r="W6" s="43">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+      <c r="X6" s="43">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+      <c r="Y6" s="43">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="Z6" s="43">
+        <f t="shared" si="2"/>
+        <v>24</v>
+      </c>
+      <c r="AA6" s="43">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="AB6" s="43">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="AC6" s="33">
+        <f t="shared" si="2"/>
+        <v>27</v>
+      </c>
+      <c r="AD6" s="33">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+      <c r="AE6" s="33">
+        <f t="shared" si="2"/>
+        <v>29</v>
+      </c>
+      <c r="AF6" s="33">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="AG6" s="33">
+        <f t="shared" si="2"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="14">
+        <v>109</v>
+      </c>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
+      <c r="S7" s="13"/>
+      <c r="T7" s="13"/>
+      <c r="U7" s="13"/>
+      <c r="V7" s="13"/>
+      <c r="W7" s="13"/>
+      <c r="X7" s="13"/>
+      <c r="Y7" s="13"/>
+      <c r="Z7" s="13"/>
+      <c r="AA7" s="13"/>
+      <c r="AB7" s="14"/>
+      <c r="AC7" s="13"/>
+      <c r="AD7" s="13"/>
+      <c r="AE7" s="13"/>
+      <c r="AF7" s="13"/>
+      <c r="AG7" s="13"/>
+    </row>
+    <row r="8" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="13">
+        <v>60</v>
+      </c>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="13"/>
+      <c r="T8" s="13"/>
+      <c r="U8" s="13"/>
+      <c r="V8" s="13"/>
+      <c r="W8" s="13"/>
+      <c r="X8" s="13"/>
+      <c r="Y8" s="13"/>
+      <c r="Z8" s="13"/>
+      <c r="AA8" s="13"/>
+      <c r="AB8" s="13"/>
+      <c r="AC8" s="13"/>
+      <c r="AD8" s="13"/>
+      <c r="AE8" s="13"/>
+      <c r="AF8" s="13"/>
+      <c r="AG8" s="13"/>
+    </row>
+    <row r="9" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="9">
+        <v>36.6</v>
+      </c>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="9"/>
+      <c r="T9" s="9"/>
+      <c r="U9" s="9"/>
+      <c r="V9" s="9"/>
+      <c r="W9" s="9"/>
+      <c r="X9" s="9"/>
+      <c r="Y9" s="9"/>
+      <c r="Z9" s="9"/>
+      <c r="AA9" s="9"/>
+      <c r="AB9" s="9"/>
+      <c r="AC9" s="9"/>
+      <c r="AD9" s="9"/>
+      <c r="AE9" s="9"/>
+      <c r="AF9" s="9"/>
+      <c r="AG9" s="9"/>
+    </row>
+    <row r="10" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="10">
+        <v>97</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="10"/>
+      <c r="T10" s="10"/>
+      <c r="U10" s="10"/>
+      <c r="V10" s="10"/>
+      <c r="W10" s="10"/>
+      <c r="X10" s="10"/>
+      <c r="Y10" s="10"/>
+      <c r="Z10" s="10"/>
+      <c r="AA10" s="10"/>
+      <c r="AB10" s="10"/>
+      <c r="AC10" s="10"/>
+      <c r="AD10" s="10"/>
+      <c r="AE10" s="10"/>
+      <c r="AF10" s="10"/>
+      <c r="AG10" s="10"/>
+    </row>
+    <row r="11" spans="2:33" ht="14" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B11" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="11">
+        <v>65</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11"/>
+      <c r="R11" s="12"/>
+      <c r="S11" s="11"/>
+      <c r="T11" s="11"/>
+      <c r="U11" s="11"/>
+      <c r="V11" s="11"/>
+      <c r="W11" s="11"/>
+      <c r="X11" s="11"/>
+      <c r="Y11" s="11"/>
+      <c r="Z11" s="11"/>
+      <c r="AA11" s="11"/>
+      <c r="AB11" s="12"/>
+      <c r="AC11" s="11"/>
+      <c r="AD11" s="11"/>
+      <c r="AE11" s="11"/>
+      <c r="AF11" s="11"/>
+      <c r="AG11" s="11"/>
+    </row>
+    <row r="12" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="26">
+        <v>65.2</v>
+      </c>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="26"/>
+      <c r="M12" s="26"/>
+      <c r="N12" s="26"/>
+      <c r="O12" s="26"/>
+      <c r="P12" s="26"/>
+      <c r="Q12" s="26"/>
+      <c r="R12" s="26"/>
+      <c r="S12" s="26"/>
+      <c r="T12" s="26"/>
+      <c r="U12" s="26"/>
+      <c r="V12" s="26"/>
+      <c r="W12" s="26"/>
+      <c r="X12" s="26"/>
+      <c r="Y12" s="26"/>
+      <c r="Z12" s="26"/>
+      <c r="AA12" s="26"/>
+      <c r="AB12" s="26"/>
+      <c r="AC12" s="26"/>
+      <c r="AD12" s="26"/>
+      <c r="AE12" s="26"/>
+      <c r="AF12" s="26"/>
+      <c r="AG12" s="26"/>
+    </row>
+    <row r="13" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="27">
+        <v>23</v>
+      </c>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="27"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="27"/>
+      <c r="N13" s="27"/>
+      <c r="O13" s="27"/>
+      <c r="P13" s="27"/>
+      <c r="Q13" s="27"/>
+      <c r="R13" s="27"/>
+      <c r="S13" s="27"/>
+      <c r="T13" s="27"/>
+      <c r="U13" s="27"/>
+      <c r="V13" s="27"/>
+      <c r="W13" s="27"/>
+      <c r="X13" s="27"/>
+      <c r="Y13" s="27"/>
+      <c r="Z13" s="27"/>
+      <c r="AA13" s="27"/>
+      <c r="AB13" s="27"/>
+      <c r="AC13" s="27"/>
+      <c r="AD13" s="27"/>
+      <c r="AE13" s="27"/>
+      <c r="AF13" s="27"/>
+      <c r="AG13" s="27"/>
+    </row>
+    <row r="14" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="27">
+        <v>47.8</v>
+      </c>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="27"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="27"/>
+      <c r="O14" s="27"/>
+      <c r="P14" s="27"/>
+      <c r="Q14" s="27"/>
+      <c r="R14" s="27"/>
+      <c r="S14" s="27"/>
+      <c r="T14" s="27"/>
+      <c r="U14" s="27"/>
+      <c r="V14" s="27"/>
+      <c r="W14" s="27"/>
+      <c r="X14" s="27"/>
+      <c r="Y14" s="27"/>
+      <c r="Z14" s="27"/>
+      <c r="AA14" s="27"/>
+      <c r="AB14" s="27"/>
+      <c r="AC14" s="27"/>
+      <c r="AD14" s="27"/>
+      <c r="AE14" s="27"/>
+      <c r="AF14" s="27"/>
+      <c r="AG14" s="27"/>
+    </row>
+    <row r="15" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="27">
+        <v>2.6</v>
+      </c>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="27"/>
+      <c r="O15" s="27"/>
+      <c r="P15" s="27"/>
+      <c r="Q15" s="27"/>
+      <c r="R15" s="27"/>
+      <c r="S15" s="27"/>
+      <c r="T15" s="27"/>
+      <c r="U15" s="27"/>
+      <c r="V15" s="27"/>
+      <c r="W15" s="27"/>
+      <c r="X15" s="27"/>
+      <c r="Y15" s="27"/>
+      <c r="Z15" s="27"/>
+      <c r="AA15" s="27"/>
+      <c r="AB15" s="27"/>
+      <c r="AC15" s="27"/>
+      <c r="AD15" s="27"/>
+      <c r="AE15" s="27"/>
+      <c r="AF15" s="27"/>
+      <c r="AG15" s="27"/>
+    </row>
+    <row r="16" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="27">
+        <v>13.5</v>
+      </c>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="27"/>
+      <c r="O16" s="27"/>
+      <c r="P16" s="27"/>
+      <c r="Q16" s="27"/>
+      <c r="R16" s="27"/>
+      <c r="S16" s="27"/>
+      <c r="T16" s="27"/>
+      <c r="U16" s="27"/>
+      <c r="V16" s="27"/>
+      <c r="W16" s="27"/>
+      <c r="X16" s="27"/>
+      <c r="Y16" s="27"/>
+      <c r="Z16" s="27"/>
+      <c r="AA16" s="27"/>
+      <c r="AB16" s="27"/>
+      <c r="AC16" s="27"/>
+      <c r="AD16" s="27"/>
+      <c r="AE16" s="27"/>
+      <c r="AF16" s="27"/>
+      <c r="AG16" s="27"/>
+    </row>
+    <row r="17" spans="2:33" ht="14" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B17" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="23">
+        <v>1363</v>
+      </c>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="23"/>
+      <c r="L17" s="23"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="23"/>
+      <c r="P17" s="23"/>
+      <c r="Q17" s="23"/>
+      <c r="R17" s="23"/>
+      <c r="S17" s="23"/>
+      <c r="T17" s="23"/>
+      <c r="U17" s="23"/>
+      <c r="V17" s="23"/>
+      <c r="W17" s="23"/>
+      <c r="X17" s="23"/>
+      <c r="Y17" s="23"/>
+      <c r="Z17" s="23"/>
+      <c r="AA17" s="23"/>
+      <c r="AB17" s="23"/>
+      <c r="AC17" s="23"/>
+      <c r="AD17" s="23"/>
+      <c r="AE17" s="23"/>
+      <c r="AF17" s="23"/>
+      <c r="AG17" s="23"/>
+    </row>
+    <row r="18" spans="2:33" ht="14" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B18" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="30"/>
+      <c r="M18" s="30"/>
+      <c r="N18" s="30"/>
+      <c r="O18" s="30"/>
+      <c r="P18" s="30"/>
+      <c r="Q18" s="30"/>
+      <c r="R18" s="30"/>
+      <c r="S18" s="30"/>
+      <c r="T18" s="30"/>
+      <c r="U18" s="30"/>
+      <c r="V18" s="30"/>
+      <c r="W18" s="30"/>
+      <c r="X18" s="30"/>
+      <c r="Y18" s="30"/>
+      <c r="Z18" s="30"/>
+      <c r="AA18" s="30"/>
+      <c r="AB18" s="30"/>
+      <c r="AC18" s="30"/>
+      <c r="AD18" s="30"/>
+      <c r="AE18" s="30"/>
+      <c r="AF18" s="30"/>
+      <c r="AG18" s="30"/>
+    </row>
+    <row r="19" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
+      <c r="L19" s="39"/>
+      <c r="M19" s="39"/>
+      <c r="N19" s="39"/>
+      <c r="O19" s="39"/>
+      <c r="P19" s="40"/>
+      <c r="Q19" s="39"/>
+      <c r="R19" s="39"/>
+      <c r="S19" s="32"/>
+      <c r="T19" s="32"/>
+      <c r="U19" s="32"/>
+      <c r="V19" s="32"/>
+      <c r="W19" s="32"/>
+      <c r="X19" s="32"/>
+      <c r="Y19" s="32"/>
+      <c r="Z19" s="40"/>
+      <c r="AA19" s="32"/>
+      <c r="AB19" s="32"/>
+      <c r="AC19" s="32"/>
+      <c r="AD19" s="40"/>
+      <c r="AE19" s="40"/>
+      <c r="AF19" s="32"/>
+      <c r="AG19" s="32"/>
+    </row>
+    <row r="20" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" s="34"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="39"/>
+      <c r="L20" s="39"/>
+      <c r="M20" s="39"/>
+      <c r="N20" s="39"/>
+      <c r="O20" s="39"/>
+      <c r="P20" s="40"/>
+      <c r="Q20" s="39"/>
+      <c r="R20" s="39"/>
+      <c r="S20" s="32"/>
+      <c r="T20" s="32"/>
+      <c r="U20" s="32"/>
+      <c r="V20" s="39"/>
+      <c r="W20" s="32"/>
+      <c r="X20" s="39"/>
+      <c r="Y20" s="32"/>
+      <c r="Z20" s="40"/>
+      <c r="AA20" s="32"/>
+      <c r="AB20" s="32"/>
+      <c r="AC20" s="32"/>
+      <c r="AD20" s="40"/>
+      <c r="AE20" s="32"/>
+      <c r="AF20" s="32"/>
+      <c r="AG20" s="32"/>
+    </row>
+    <row r="21" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" s="32"/>
+    </row>
+    <row r="22" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" s="34" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" s="31" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24" s="35" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25" s="35"/>
+    </row>
+    <row r="26" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B26" s="42" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B27" s="50"/>
+    </row>
+    <row r="28" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B28" s="50"/>
+    </row>
+    <row r="29" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29" s="50"/>
+    </row>
+    <row r="30" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B30" s="49"/>
+    </row>
+    <row r="31" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B31" s="49"/>
+    </row>
+    <row r="32" spans="2:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B32" s="49"/>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B33" s="49"/>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B34" s="51"/>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B35" s="51"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0" right="0" top="0.74803149606299213" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="83" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+</worksheet>
 </file>